--- a/dashboard/dashboard_hanh_dong_v2.xlsx
+++ b/dashboard/dashboard_hanh_dong_v2.xlsx
@@ -1,16 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard Hành Động" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nhật ký Thay đổi v1 sang v2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Dashboard Hành Động" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Nhật ký Thay đổi v1 sang v2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Định nghĩa đo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Gate 30-60-90" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Bằng chứng" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dashboard Hành Động'!$A$4:$H$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Dashboard Hành Động'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Dashboard Hành Động'!$A$1:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Nhật ký Thay đổi v1 sang v2'!$A$4:$F$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Nhật ký Thay đổi v1 sang v2'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Nhật ký Thay đổi v1 sang v2'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Định nghĩa đo'!$A$4:$E$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Định nghĩa đo'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Định nghĩa đo'!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Gate 30-60-90'!$A$4:$E$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Gate 30-60-90'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Gate 30-60-90'!$A$1:$E$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bằng chứng'!$A$4:$E$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Bằng chứng'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Bằng chứng'!$A$1:$E$11</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +37,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,8 +74,25 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="0017365D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0017365D"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -81,8 +117,28 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0017365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F6FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -118,11 +174,16 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9E2F3"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,6 +211,27 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -514,340 +596,362 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="73" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>DASHBOARD HÀNH ĐỘNG CHO ÁP DỤNG AI (AI ADOPTION ACTION DASHBOARD) - BẢN V2 (SAU PHẢN BIỆN CHÉO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Dự án: Trợ lý AI Tra cứu Quy trình Nội bộ | Nhóm: Promt Kiếm Tông (Day26_Track01_Promt_Kiem_Tong) | TV: Trần Đình Hinh, Hoàng Quốc Dũng, Đinh Xuân Quyền</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Tầng đo lường (5 Tầng)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>DASHBOARD HÀNH ĐỘNG ÁP DỤNG AI — V2 HIỆU CHỈNH THEO YEUCAU.MD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="56" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Promt Kiếm Tông | Baseline chưa có bằng chứng kèm theo; mọi mục tiêu là đề xuất, xác nhận tại Gate 30 | Xem Định nghĩa đo, Gate 30-60-90, Bằng chứng</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="n"/>
+      <c r="B3" s="12" t="n"/>
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="12" t="n"/>
+      <c r="G3" s="12" t="n"/>
+      <c r="H3" s="12" t="n"/>
+    </row>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Tầng đo lường</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Loại chỉ số</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Tên chỉ số cụ thể</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Mốc ban đầu (Baseline)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Mục tiêu (Target 30-60-90)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Nguồn dữ liệu (Log/Hệ thống)</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Người phụ trách (Owner)</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Hành động cụ thể khi chỉ số xấu</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Tên chỉ số</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Baseline / trạng thái</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Mục tiêu và kỳ đánh giá</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Nguồn dữ liệu</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Owner nghiệp vụ cần xác nhận</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Hành động khi chỉ số xấu</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="180" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Tầng 1: Sử dụng</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Workflow-level</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Tỷ lệ chuyên viên vận hành ứng dụng AI vào ca trực hàng tuần</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>18% (Tuần 1 pilot)</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Gate 30: ≥ 60%
-Gate 60: ≥ 85%</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Audit log phiên làm việc tích hợp trên hệ thống Helpdesk</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Trần Đình Hinh (Trưởng ca Vận hành)</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Phỏng vấn 1-1 ngay trong 24h đối với chuyên viên không dùng; kiểm tra xem có gặp lỗi kỹ thuật hoặc thiếu tài liệu chuyên môn không.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Tỷ lệ người có tác vụ AI thực sự gắn với workflow trong tuần</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Đo tại Gate 30. Bản nhóm ghi 18%, chưa xác minh; kỳ đo và mẫu số chưa thống nhất. Không gọi đây là tỷ lệ adoption.</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Gate 30: khóa baseline.
+Gate 60/90: ≥85% người có tác vụ đủ điều kiện trong tuần. Đối chiếu số người thực tế, không suy từ 18% của 25 người.</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Log tác vụ AI có ticket_id + lịch phân công/tác vụ đủ điều kiện; không chỉ dùng log đăng nhập.</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Chủ quy trình Vận hành</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>Dưới 85% ở Gate 60/90: trong 24 giờ làm việc kiểm lỗi truy cập, thiếu nguồn và điểm vướng với người chưa dùng; sửa/hỗ trợ trong workflow, đo lại tuần kế tiếp. Không nhắc tăng prompt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="180" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Tầng 2: Hành vi</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Workflow-level</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Tỷ lệ tra cứu thành công không cần hỏi lại đồng nghiệp</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>22% (Hiện trạng hỏi người)</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Gate 30: ≥ 60%
-Gate 60: ≥ 80%</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Micro-survey 1 chạm sau phiên tra cứu + Log ticket hoàn tất</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Đinh Xuân Quyền (Quản lý Quy trình)</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Lọc danh sách các câu hỏi phải chuyển người; nếu do thiếu tài liệu -&gt; Giao Data Owner bổ sung văn bản vào kho trong 24h.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Tỷ lệ tác vụ AI hoàn tất đã duyệt, không hỏi thêm và không phải sửa trong 2 ngày làm việc</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Đo tại Gate 30. Bản nhóm ghi 22%, chưa có mẫu/log kiểm chứng.</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Gate 30: khóa baseline.
+Gate 60/90: ≥80% tác vụ đủ thời gian theo dõi.</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>Log trạng thái ticket, dấu duyệt, sự kiện hỏi thêm/chuyển người/làm lại; micro-survey chỉ bổ trợ, đối chiếu với log.</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>Chủ quy trình Vận hành</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>Dưới 80%: phân loại ca hỏi lại/làm lại trong 24 giờ làm việc; Data Owner xử lý thiếu nguồn hoặc khóa nguồn lỗi; Chủ quy trình sửa hướng dẫn/điểm bàn giao. Giữ chuyển người an toàn, không ép giảm handoff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="180" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Tầng 3: Năng suất</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Workflow-level</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Thời gian trung bình hoàn thành một lượt tra cứu (Xử lý ticket)</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>8.5 phút (Tra cứu file thủ công)</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Gate 30: ≤ 5.0 phút
-Gate 60: ≤ 3.0 phút</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Log thời gian thao tác từ khi mở ticket đến đóng ticket trên Helpdesk</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Trần Đình Hinh (Chủ quy trình Vận hành)</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Rà soát video screen-recording mẫu: Xác định nhân viên mất thời gian ở bước đọc hiểu hay bước kiểm chứng; tối ưu giao diện hiển thị trích dẫn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Tầng 4: Chất lượng &amp; Độ tin cậy</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Phút lao động chủ động trung bình để hoàn tất một lượt tra cứu đã kiểm chứng</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Đo ≥50 lượt thủ công tương đương tại Gate 30. Bản nhóm ghi 8,5 phút, chưa xác minh.</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Gate 30: khóa baseline theo loại tác vụ.
+Gate 60/90: ≤3,0 phút/lượt. Cộng công sức mọi người, chuyển/làm lại trong 2 ngày làm việc.</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Sự kiện bắt đầu/kết thúc từng đoạn tra cứu, duyệt, chuyển/làm lại gắn cùng ticket_id; không dùng thời gian mở → đóng toàn bộ ticket.</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Chủ quy trình Vận hành</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>Trên 3,0 phút: trong 48 giờ làm việc phân tích các đoạn tra cứu/đọc/kiểm chứng/chuyển giao theo loại tác vụ; điều chỉnh nguồn hoặc giao diện; đo lại. Không bỏ bước kiểm nguồn để đạt mục tiêu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="180" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Tầng 4: Chất lượng &amp; tin cậy</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Product-level</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Tỷ lệ câu trả lời AI có đính kèm trích dẫn văn bản, điều khoản &amp; ngày hiệu lực chính xác</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>0% (Bản v1 không trích dẫn)</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Gate 30: ≥ 95%
-Gate 60: ≥ 98%</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>QA ngẫu nhiên 50 câu/tuần + Log trích dẫn metadata của hệ thống RAG</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Hoàng Quốc Dũng (AI Tech Lead)</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>KÍCH HOẠT SLA KHẨN CẤP: Tạm dừng cập nhật tài liệu mới; rà soát pipeline re-ranking và semantic chunking; hiệu chỉnh system prompt sinh trích dẫn trong 48h.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Tầng 4: Chất lượng &amp; Độ tin cậy</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Tỷ lệ câu trả lời chính sách có nội dung, trích dẫn và hiệu lực nguồn đúng</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>QA đo tại Gate 30. Bản nhóm ghi 0%, chưa có tập đánh giá; thiếu dữ liệu không đồng nghĩa 0%.</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Gate 30: ≥95% trên bộ thử ≥100 câu, gồm ≥20 ca cần chuyển.
+Gate 60/90: ≥98% trên mẫu QA ngẫu nhiên hằng tuần; ca từ chối không vào mẫu số trả lời chính sách.</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Log RAG + phiếu QA đối chiếu nguồn gốc/điều khoản/hiệu lực và quyền mở link. QA độc lập ≥50 câu/tuần, ít hơn thì kiểm toàn bộ.</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>AI Tech Lead; QA đánh giá độc lập</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Dưới ngưỡng gate: khóa nguồn/luồng bị ảnh hưởng, Data Owner kiểm hiệu lực; AI Tech Lead rà retrieval/index/citation trong 48 giờ làm việc; QA chạy lại trước mở. Sai chính sách nghiêm trọng hoặc sai quyền: dừng luồng ngay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="180" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Tầng 4: Chất lượng &amp; tin cậy</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Product-level</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Tỷ lệ câu hỏi không chắc chắn (&lt;85% confidence) được chuyển giao chuyên viên kèm tóm tắt ngữ cảnh</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>0% (Chưa có cơ chế Handoff)</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>100% (Mọi ca không chắc đều được chuyển người)</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Log định tuyến Handoff &amp; hàng đợi ticket chuyên gia</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Hoàng Quốc Dũng &amp; Đinh Xuân Quyền</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Họp khẩn cấp rà soát ngưỡng tự tin (confidence threshold); kiểm tra trường hợp AI tự bịa câu trả lời (hallucination) để siết chặt bộ lọc an toàn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Tầng 5: Giá trị nghiệp vụ</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Business Value</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Tổng số giờ lao động nghiệp vụ tiết kiệm được thực tế của phòng Vận hành</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>0 giờ/tháng</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Gate 30: ≥ 40 giờ/tháng
-Gate 60: ≥ 120 giờ/tháng</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>Báo cáo phân tích hiệu suất lao động Helpdesk (Thời gian tiết kiệm x Số lượng ticket)</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Trần Đình Hinh (Trưởng phòng Vận hành)</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Họp Gate Review cấp Khối: Đánh giá khả năng hấp thụ (Absorption); nếu không đạt tối thiểu 60 giờ/tháng ở Gate 60 -&gt; Tạm dừng dự án để tái thẩm định ROI.</t>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Tỷ lệ ca cần chuyển người được bàn giao đủ ngữ cảnh, đúng người, nhận trong SLA</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Đo tại Gate 30. Bản nhóm ghi 0%, chưa có log. Không có ca cần chuyển thì N/A, không ghi 100%.</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Gate 30: 100% ca cần chuyển trong bộ thử (≥20 ca).
+Gate 60/90: 100% ca cần chuyển phát hiện qua log + QA; nhận trong 4 giờ làm việc. Không có ca thật: N/A và báo riêng bộ thử.</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>Log định tuyến, ticket_id, lý do, ngữ cảnh, người nhận/thời điểm nhận + QA rà cả ca không chuyển để tìm bỏ sót.</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Chủ quy trình Vận hành; AI Tech Lead phụ trách định tuyến</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>Bỏ sót/thiếu ngữ cảnh/quá 4 giờ: chuyển thủ công ngay và báo Chủ quy trình; rà định tuyến, cảnh báo và hàng đợi trong 24 giờ làm việc. Thiếu/mâu thuẫn/hết hiệu lực nguồn, ngoài phạm vi hoặc nghi sai đều là trigger, không dùng điểm tự tin 85%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="180" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Tầng 5: Giá trị</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Workflow-level / Business Value</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Tổng giờ lao động tiết kiệm ròng trong tháng của các workflow đã khóa</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Chưa xác định; khóa baseline và lưu lượng tại Gate 30. Không tự đặt 0 giờ khi chưa đo.</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Gate 30: xác nhận lưu lượng và tính khả thi.
+Gate 60/90: ≥120 giờ ròng/tháng trên một tháng đủ dữ liệu. Đây là mục tiêu, chưa phải kết quả/ROI.</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Log tác vụ cùng loại × baseline đã xác nhận; phút thực tế mọi người, làm lại/chuyển người; sổ công QA, hỗ trợ, bảo trì tăng thêm. Xem Định nghĩa đo.</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>Chủ quy trình Vận hành</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>Dưới 120 giờ/tháng: so khối lượng, công sức và baseline, sửa rồi đo lại, chưa mở rộng. Nếu ròng ≤0 trong 4 tuần đủ mẫu sau một vòng sửa, trình đề xuất dừng. Không cắt QA để làm đẹp số.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:H10"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;CPromt Kiếm Tông | V2 hiệu chỉnh | Trang &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -855,166 +959,936 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
+    <col width="57" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BẢNG ĐỐI CHIẾU THAY ĐỔI GIỮA BẢN V1 VÀ BẢN V2 (SAU PHẢN BIỆN CHÉO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Dự án: Trợ lý AI Tra cứu Quy trình | Nhóm: Promt Kiếm Tông | Căn cứ tiêu chí đánh giá Lab Day 26 (Bắt buộc ≥ 2 thay đổi sau phản biện)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>ĐỐI CHIẾU V1 → V2 — GIỮ NGUYÊN FILE V1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="56" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Góp ý Nhóm 05 theo bản nhóm ghi, chưa kèm biên bản. Các sửa rà soát bổ sung không được gán thành góp ý Nhóm 05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="n"/>
+      <c r="B3" s="12" t="n"/>
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="12" t="n"/>
+    </row>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Hạng mục thay đổi</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>Nội dung Bản v1 (Cũ)</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>Nội dung Bản v2 (Mới)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Góp ý từ nhóm bạn (Nhóm 05)</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>Lý do &amp; Tác động thực tế</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="65" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="170" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Chỉ số tầng 1 &amp; 4 (Loại bỏ Activity, tăng Quality)</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Đo 'Số lượng prompt/ngày' và 'Nút Like/Dislike'</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Thay bằng: 'Tỷ lệ câu trả lời có trích dẫn văn bản, điều khoản chính xác ≥ 95%' và 'Tỷ lệ tra cứu thành công không cần hỏi lại đồng nghiệp ≥ 80%'</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Chỉ số prompt là activity metric ảo; người dùng hỏi nhiều có thể vì AI trả lời sai. Nút like là cảm tính, không đo được tính pháp lý.</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Đưa chỉ số về đúng tầng Chất lượng &amp; Tin cậy; giải quyết triệt để điểm nghẽn Desire theo ADKAR (nhân viên chỉ dám dùng khi có trích nguồn).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Chất lượng thay activity</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>V1 C5: số prompt/ngày; C9: tỷ lệ Like.</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>V2 C8: trích nguồn đúng; C6: tác vụ hoàn tất không hỏi thêm/làm lại. Bỏ prompt và Like.</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Theo bản nhóm: prompt cao/Like không chứng minh chất lượng; cần biên bản xác nhận.</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Chuyển sang chất lượng và kết quả thực của workflow; không gọi activity là vô dụng trong mọi mục đích.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Cơ chế Rủi ro &amp; Bàn giao (Handoff)</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Không có cơ chế chuyển giao người khi AI không chắc; chỉ có nút Dislike chung chung.</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Bổ sung chỉ số &amp; tính năng: Tự động chuyển giao 100% ca truy vấn có độ tự tin &lt;85% sang chuyên viên cấp cao kèm tóm tắt ngữ cảnh.</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Cần có chốt chặn an toàn khi AI gặp câu hỏi phức tạp hoặc dữ liệu chưa cập nhật, tránh trường hợp nhân viên tự mò mẫm.</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Tuân thủ triệt để nguyên lý Mollick (Con người giữ quyền phán quyết cuối cùng); ngăn chặn rủi ro tư vấn sai chính sách nghiệp vụ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Rủi ro và bàn giao</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>V1 chưa có chỉ số handoff.</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>V2 C9: ca cần chuyển có ticket đủ ngữ cảnh, đúng người và được nhận trong 4 giờ làm việc.</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Theo bản nhóm: cần chốt chặn khi câu hỏi phức tạp hoặc nguồn thiếu; chưa kèm biên bản.</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>Mollick: người giữ quyền; QA phát hiện cả ca đáng ra phải chuyển nhưng bị bỏ sót.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="170" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Quy tắc khi chỉ số xấu &amp; SLA vận hành</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Hành động chung chung: 'Nhắc nhở nhân viên', 'Gửi email', 'Họp xem xét'.</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Quy định rõ SLA: Trong 24h đối với micro-survey; tạm dừng nạp dữ liệu và xử lý trong 48h đối với lỗi trích nguồn; bổ nhiệm Data Owner cập nhật văn bản thứ 6 hàng tuần.</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Chỉ số phải dẫn tới hành động cụ thể, có thời hạn và có người chịu trách nhiệm rõ ràng.</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Đảm bảo khả năng hấp thụ (Absorption theo Gartner-Lite) và tính thực thi trong môi trường vận hành thực tế.</t>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Nguồn đo và giá trị</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>V1 F8: thời gian tự khai; F10: giờ tiết kiệm lý thuyết.</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>V2 F7/F10: log riêng bước tra cứu; tính ròng sau QA, hỗ trợ, bảo trì và làm lại.</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Theo bản nhóm: chỉ số cần nguồn thực tế; cần xác nhận nội dung phản biện nhận về.</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Chưa có baseline thì không báo kết quả. 120 giờ/tháng là mục tiêu đề xuất.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="170" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Ownership và SLA</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>V1 H5/H8: email nhắc dùng, họp phòng ban; chưa có Data Owner trong dashboard.</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>V2: Data Owner duyệt nguồn, lịch kiểm hằng tuần; SLA 24/48 giờ; điều kiện sửa/dừng cụ thể.</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Theo bản nhóm: hành động cần owner/thời hạn; cần biên bản.</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Phân biệt vai trò đơn vị vận hành với thành viên điều phối bài nhóm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="170" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Hiệu chỉnh theo yêu cầu 16/10/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Các file v2 cũ lệch target, kỳ đo 18%, mô tả 65%; thiếu nguồn số liệu.</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Thống nhất 6 chỉ số/5 tầng; ghi chưa xác minh, định nghĩa mẫu/gate; bỏ confidence 85% và accuracy 99% chưa kiểm định.</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Rà soát bổ sung theo Yeucau.md; không gán cho Nhóm 05.</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>V1 không sửa. Cần nhóm bổ sung case thực tế và bằng chứng trước khi xác nhận đạt toàn bộ đề bài.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:F9"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;CPromt Kiếm Tông | V2 hiệu chỉnh | Trang &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="67" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>ĐỊNH NGHĨA VÀ QUY TẮC ĐO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="56" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Mục tiêu đề xuất, baseline chờ xác nhận. Ngưỡng gate phải đồng thời đạt; thiếu dữ liệu không coi là đạt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="n"/>
+      <c r="B3" s="12" t="n"/>
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+    </row>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Chỉ số / ô dashboard</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Công thức</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Mẫu / kỳ đo</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Thiếu dữ liệu / tránh sai lệch</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Nguồn / ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="170" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Mức dùng (C5)</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Số người có ≥1 tác vụ AI thực sự gắn ticket / số người có tác vụ đủ điều kiện được phân công trong tuần ×100%.</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Người, theo tuần. Ghi cả tử/mẫu số; so log với lịch phân công, không dùng login thay tác vụ.</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Mẫu số=0 → N/A. Quy mô 25 theo bài nhóm, phải xác nhận; không suy số người từ 18%.</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Chủ quy trình xác nhận phạm vi và ngày đo tại Gate 30. Đây là usage trong workflow, không phải adoption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Hành vi (C6)</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Tác vụ AI hoàn tất đã duyệt, không hỏi thêm/không sửa trong 2 ngày làm việc / toàn bộ tác vụ AI đủ thời gian theo dõi ×100%.</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Tác vụ, tuần; theo dõi thêm 2 ngày làm việc sau mốc báo cáo; ≥50 tác vụ/tuần để xét Gate 60/90.</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Chưa xong/thiếu trạng thái → không tính thành công. Thiếu log không tự coi là không sửa. Survey thiếu không được tùy ý loại khỏi mẫu số.</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Đối chiếu phản hồi với log. Ca chuyển chuyên viên không vào tử số nhưng an toàn bàn giao luôn được ưu tiên.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="170" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Năng suất (C7)</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Tổng phút lao động chủ động của mọi người ở các đoạn tra cứu, kiểm chứng, chuyển/làm lại / số tác vụ tương ứng.</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Baseline ≥50 lượt thủ công tương đương theo loại/độ khó, rồi áp dụng trọng số cơ cấu tác vụ thực tế. Pilot ≥50 tác vụ đủ theo dõi/tuần.</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Không lấy thời gian đóng cả ticket. Không bỏ ca thất bại để giảm trung bình. Báo riêng ca chưa xong, phút chờ, tỷ lệ thiếu log; thiếu dữ liệu thì chưa đủ căn cứ qua gate.</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Lưu ticket_id, loại, bắt đầu/kết thúc từng đoạn, người duyệt và sửa trong 2 ngày. Không cộng trùng đoạn song song của cùng người.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="170" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Trích nguồn (C8)</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Câu trả lời đạt đồng thời: nội dung/điều khoản đúng, link có quyền mở, nguồn đang hiệu lực / câu trả lời chính sách trong mẫu ngẫu nhiên ×100%.</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Gate 30: bộ thử ≥100 câu, ≥20 ca cần chuyển; tỷ lệ trích nguồn tính trên câu trả lời chính sách, số ca từ chối báo riêng. Gate 60/90: ngẫu nhiên ≥50 câu/tuần hoặc toàn bộ nếu ít hơn.</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Không có câu trả lời chính sách → N/A, không báo 100%. Từ chối theo dõi ở handoff; ca trả lời đáng ra phải từ chối được QA đánh lỗi.</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>QA độc lập chấm với nguồn chuẩn. Kiểm riêng toàn bộ ca lỗi/handoff, không trộn mẫu chọn thêm vào mẫu ngẫu nhiên.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="170" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Bàn giao (C9)</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Ca cần chuyển có ticket đủ ngữ cảnh, đúng người, được nhận trong 4 giờ làm việc / toàn bộ ca cần chuyển phát hiện qua log và QA ×100%.</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Thiếu/mâu thuẫn/hết hiệu lực nguồn, ngoài phạm vi, người dùng nghi sai. Bộ thử Gate 30 có ≥20 ca. Vận hành: rà toàn bộ ca được gắn cờ và QA ca chưa chuyển.</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Không ca thật → N/A, báo kết quả bộ thử riêng. Bộ thử phải đạt; không tuyên bố 100% vận hành nếu không phát sinh ca. Ca bị bỏ sót vẫn vào mẫu số khi QA phát hiện.</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Nguồn bằng chứng: ticket_id, câu hỏi, nguồn, lý do, người nhận, thời điểm tạo/nhận. SLA tính giờ làm việc theo lịch đơn vị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="170" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Giờ ròng (C10)</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>[Σ(baseline phút đúng loại tác vụ) − Σ(phút thực tế mọi người, chuyển/làm lại) − phút QA/hỗ trợ/bảo trì tăng thêm] /60.</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Một tháng đủ dữ liệu, cùng phạm vi tác vụ/độ khó với baseline; báo lưu lượng và công sức tăng thêm. Gate 30 kiểm tính khả thi, Gate 60/90 ≥120 giờ/tháng.</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Không có baseline/thiếu công sức bổ sung → chưa xác định; không ghi 0 hoặc 120 như thực đo. Không trừ hai lần phần đã tính trong phút tác vụ.</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Ví dụ giả định: (8,5−3,0)=5,5 phút/lượt; ceil(120×60/5,5)=1.310 lượt trước QA/hỗ trợ. Không tự suy ROI hoặc tiết kiệm tiền mặt.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:E10"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;CPromt Kiếm Tông | V2 hiệu chỉnh | Trang &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="67" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>GATE DỰA TRÊN BẰNG CHỨNG, KHÔNG CHỈ THEO LỊCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="56" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Vai trò nghiệp vụ cần được đơn vị xác nhận; sinh viên chỉ điều phối bài nhóm. Mục tiêu phải xác nhận ở Gate 30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="n"/>
+      <c r="B3" s="12" t="n"/>
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+    </row>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Giai đoạn</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Owner chịu trách nhiệm</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Công việc / bằng chứng</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Điều kiện chuyển</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Nếu chưa đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="170" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>0–30: chứng minh vấn đề và readiness</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Chủ quy trình Vận hành; Data Owner, QA, AI Tech Lead thực hiện</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Xác nhận case thật; khóa phạm vi/nguồn, bổ nhiệm owner; duyệt quyền, ngân sách, hỗ trợ và nơi lưu log. Baseline ≥50 lượt thủ công tương đương; bộ thử ≥100 câu gồm ≥20 ca cần chuyển.</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Trích nguồn ≥95%; bàn giao đúng 100% ca thử; đủ baseline/owner/nguồn lực; không lỗi nghiêm trọng chưa xử lý. Mức dùng, hành vi, thời gian và giờ ròng: khóa baseline/kiểm tính khả thi, chưa đặt kết quả đã đạt.</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Thiếu điều kiện/mẫu → sửa/đo tiếp, chưa mở pilot AI trong workflow. Hết 30 ngày không tự qua gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>31–60: chất lượng, hành vi và giá trị</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Chủ quy trình Vận hành; QA độc lập xác nhận</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Pilot trong nhóm đã khóa. ≥50 tác vụ đủ theo dõi/tuần trong 2 tuần liên tiếp; QA ngẫu nhiên ≥50 câu/tuần hoặc toàn bộ nếu ít hơn. Một tháng đủ dữ liệu giờ ròng.</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Đồng thời: mức dùng ≥85%; hành vi ≥80%; thời gian ≤3,0 phút; trích nguồn ≥98%; bàn giao 100%; giờ ròng ≥120/tháng; không lỗi nghiêm trọng chưa xử lý. Không có ca handoff thật: N/A + bộ thử đạt, chưa kết luận tỷ lệ vận hành.</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Thiếu mục tiêu/mẫu → chưa mở rộng; sửa có owner/hạn xử lý rồi đo lại. Lỗi nghiêm trọng: dừng luồng ngay, QA thử lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="170" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>61–90: quyết định mở rộng</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Chủ quy trình trình Ban Điều hành; Data Owner, QA, AI Tech Lead bàn giao</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Duy trì mọi ngưỡng Gate 60 trong 4 tuần liên tiếp, cùng yêu cầu mẫu. Một tháng đủ dữ liệu giờ ròng. Chốt owner vận hành, hỗ trợ, quyền và ngân sách phạm vi mới.</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Đạt đủ → đề xuất mở rộng từng đợt sau phê duyệt; không tự đặt quy mô 200 người hoặc tuyên bố normalization.</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Không đạt → giữ/sửa pilot; ròng ≤0 trong 4 tuần đủ mẫu sau một vòng sửa hoặc không khắc phục quyền/nguồn lực → trình đề xuất dừng.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:E7"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;CPromt Kiếm Tông | V2 hiệu chỉnh | Trang &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="67" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>TRẠNG THÁI BẰNG CHỨNG VÀ VIỆC CẦN NHÓM BỔ SUNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="56" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Nhóm xác nhận chưa có bằng chứng kèm theo khi rà soát. Không công bố log nhạy cảm; dùng bản tổng hợp đã ẩn danh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="n"/>
+      <c r="B3" s="12" t="n"/>
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+    </row>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Nội dung</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Hiện có</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Cần bổ sung / giới hạn</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Người điều phối</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="170" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Case thực tế và 25 người</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả tình huống trong bài nhóm; chưa có căn cứ đính kèm.</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Chưa xác minh</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Xác nhận tình huống từ lớp/doanh nghiệp; nguồn ghi nhận, thời điểm, phạm vi. Không dùng case tưởng tượng theo §3.1.</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Trần Đình Hinh điều phối; Chủ quy trình xác nhận.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>18% quay lại</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>README: sau 2 tuần; memo cũ: sau 4 tuần; Excel cũ: tuần 1.</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Chưa xác minh; không khớp kỳ đo, thiếu tử/mẫu số</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Định nghĩa quay lại, ngày đo và số người đủ điều kiện. 18% không tương ứng số nguyên người trên 25; không sửa thành số mới khi thiếu log.</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Trần Đình Hinh điều phối, đối chiếu log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="170" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>8,5 phút; 22%; trích nguồn/handoff 0%</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Có số trong bản nhóm, chưa có tập đo.</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Chưa xác minh; baseline hiện tại phải đo lại/xác nhận</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Log tác vụ đã ẩn danh, phương pháp đo theo Định nghĩa đo; thiếu dữ liệu không suy ra 0%.</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Đinh Xuân Quyền tổng hợp; Hoàng Quốc Dũng cùng QA đối chiếu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="170" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>65%; 450 phiên; phỏng vấn 10/10</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Các bản mô tả khác nhau về kỳ và tiêu chí bỏ dở; chưa có log/ghi nhận.</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Chưa xác minh; không dùng làm kết quả đã chứng minh</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Đính kèm bản tổng hợp có ngày, mẫu, định nghĩa, câu hỏi phỏng vấn và người tổng hợp; không tự tạo lời trích dẫn.</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Nhóm trưởng xác nhận với người thu thập.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="170" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Phản biện Nhóm 05</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Có mô tả góp ý trong bài, chưa kèm biên bản.</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Theo bài nhóm ghi; chưa xác minh</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Ghi riêng góp ý đã đưa đi và ≥2 góp ý nhận về, người tham gia và sửa tương ứng. V1 được giữ nguyên để đối chiếu.</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Nhóm trưởng xác nhận.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="170" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Case tham khảo Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>https://openai.com/index/morgan-stanley/</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Đã kiểm tra nguồn ngày 16/10/2026</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Nguồn mô tả eval trước triển khai, chuyên gia chấm, QA hồi quy và người kiểm. Hỗ trợ lựa chọn thiết kế, không xác nhận hiện trạng nội bộ hoặc quan hệ nhân quả riêng của citations.</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Suy luận áp dụng của nhóm, không phải log doanh nghiệp nhóm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="170" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Mục tiêu ≥120 giờ/tháng</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Chưa có baseline, lưu lượng và công sức tăng thêm.</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Mục tiêu đề xuất; chưa phải kết quả/ROI</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Kiểm định lượng tác vụ và phút tiết kiệm ròng; chốt mục tiêu có thể thu thập và nguồn lực tại Gate 30.</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Chủ quy trình Vận hành phê duyệt.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:E11"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId1"/>
+  </hyperlinks>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;CPromt Kiếm Tông | V2 hiệu chỉnh | Trang &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/dashboard/dashboard_hanh_dong_v2.xlsx
+++ b/dashboard/dashboard_hanh_dong_v2.xlsx
@@ -11,24 +11,24 @@
     <sheet name="Nhật ký Thay đổi v1 sang v2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Định nghĩa đo" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Gate 30-60-90" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Bằng chứng" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Kế hoạch dữ liệu" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dashboard Hành Động'!$A$4:$H$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Dashboard Hành Động'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Dashboard Hành Động'!$A$1:$H$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Nhật ký Thay đổi v1 sang v2'!$A$4:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Nhật ký Thay đổi v1 sang v2'!$A$4:$F$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Nhật ký Thay đổi v1 sang v2'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Nhật ký Thay đổi v1 sang v2'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Nhật ký Thay đổi v1 sang v2'!$A$1:$F$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Định nghĩa đo'!$A$4:$E$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Định nghĩa đo'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Định nghĩa đo'!$A$1:$E$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Gate 30-60-90'!$A$4:$E$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Gate 30-60-90'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Gate 30-60-90'!$A$1:$E$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bằng chứng'!$A$4:$E$11</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Bằng chứng'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Bằng chứng'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Kế hoạch dữ liệu'!$A$4:$E$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Kế hoạch dữ liệu'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Kế hoạch dữ liệu'!$A$1:$E$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -614,14 +614,14 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>DASHBOARD HÀNH ĐỘNG ÁP DỤNG AI — V2 HIỆU CHỈNH THEO YEUCAU.MD</t>
+          <t>DASHBOARD HÀNH ĐỘNG ÁP DỤNG AI — BẢN V2</t>
         </is>
       </c>
     </row>
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Promt Kiếm Tông | Baseline chưa có bằng chứng kèm theo; mọi mục tiêu là đề xuất, xác nhận tại Gate 30 | Xem Định nghĩa đo, Gate 30-60-90, Bằng chứng</t>
+          <t>Dự án: Trợ lý AI tra cứu quy trình &amp; chính sách nội bộ | Nhóm: Promt Kiếm Tông | Baseline thu thập tại Gate 30</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Baseline / trạng thái</t>
+          <t>Mốc ban đầu (Baseline)</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>Owner nghiệp vụ cần xác nhận</t>
+          <t>Người phụ trách (Owner)</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -695,13 +695,13 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Đo tại Gate 30. Bản nhóm ghi 18%, chưa xác minh; kỳ đo và mẫu số chưa thống nhất. Không gọi đây là tỷ lệ adoption.</t>
+          <t>Thu thập tại Gate 30 từ log tác vụ và lịch phân công; ghi rõ số người sử dụng và số người có tác vụ đủ điều kiện.</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Gate 30: khóa baseline.
-Gate 60/90: ≥85% người có tác vụ đủ điều kiện trong tuần. Đối chiếu số người thực tế, không suy từ 18% của 25 người.</t>
+Gate 60/90: ≥85% người có tác vụ đủ điều kiện trong tuần.</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>Dưới 85% ở Gate 60/90: trong 24 giờ làm việc kiểm lỗi truy cập, thiếu nguồn và điểm vướng với người chưa dùng; sửa/hỗ trợ trong workflow, đo lại tuần kế tiếp. Không nhắc tăng prompt.</t>
+          <t>Dưới 85% ở Gate 60/90: trong 24 giờ làm việc kiểm lỗi truy cập, thiếu nguồn và điểm vướng với người chưa dùng; sửa/hỗ trợ trong workflow, đo lại tuần kế tiếp.</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>Đo tại Gate 30. Bản nhóm ghi 22%, chưa có mẫu/log kiểm chứng.</t>
+          <t>Thu thập tại Gate 30 từ log hoàn tất, hỏi thêm và làm lại; theo dõi thêm 2 ngày làm việc.</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>Đo ≥50 lượt thủ công tương đương tại Gate 30. Bản nhóm ghi 8,5 phút, chưa xác minh.</t>
+          <t>Đo ≥50 lượt tra cứu thủ công tương đương tại Gate 30, phân theo loại tác vụ và độ khó.</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>QA đo tại Gate 30. Bản nhóm ghi 0%, chưa có tập đánh giá; thiếu dữ liệu không đồng nghĩa 0%.</t>
+          <t>QA đo tại Gate 30 trên bộ câu hỏi kiểm thử, đối chiếu nội dung, điều khoản và hiệu lực nguồn.</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>Đo tại Gate 30. Bản nhóm ghi 0%, chưa có log. Không có ca cần chuyển thì N/A, không ghi 100%.</t>
+          <t>Thu thập tại Gate 30 từ log định tuyến và kiểm thử các ca cần chuyển người. Không phát sinh ca thực tế: N/A.</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>Bỏ sót/thiếu ngữ cảnh/quá 4 giờ: chuyển thủ công ngay và báo Chủ quy trình; rà định tuyến, cảnh báo và hàng đợi trong 24 giờ làm việc. Thiếu/mâu thuẫn/hết hiệu lực nguồn, ngoài phạm vi hoặc nghi sai đều là trigger, không dùng điểm tự tin 85%.</t>
+          <t>Bỏ sót/thiếu ngữ cảnh/quá 4 giờ: chuyển thủ công ngay và báo Chủ quy trình; rà định tuyến, cảnh báo và hàng đợi trong 24 giờ làm việc. Thiếu/mâu thuẫn/hết hiệu lực nguồn, ngoài phạm vi hoặc nghi sai đều kích hoạt chuyển người.</t>
         </is>
       </c>
     </row>
@@ -910,13 +910,13 @@
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>Chưa xác định; khóa baseline và lưu lượng tại Gate 30. Không tự đặt 0 giờ khi chưa đo.</t>
+          <t>Xác định tại Gate 30 từ baseline thời gian, lưu lượng tác vụ và công sức QA/hỗ trợ/bảo trì.</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Gate 30: xác nhận lưu lượng và tính khả thi.
-Gate 60/90: ≥120 giờ ròng/tháng trên một tháng đủ dữ liệu. Đây là mục tiêu, chưa phải kết quả/ROI.</t>
+Gate 60/90: ≥120 giờ ròng/tháng trên một tháng đủ dữ liệu.</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>Dưới 120 giờ/tháng: so khối lượng, công sức và baseline, sửa rồi đo lại, chưa mở rộng. Nếu ròng ≤0 trong 4 tuần đủ mẫu sau một vòng sửa, trình đề xuất dừng. Không cắt QA để làm đẹp số.</t>
+          <t>Dưới 120 giờ/tháng: so khối lượng, công sức và baseline, sửa rồi đo lại, chưa mở rộng. Nếu ròng ≤0 trong 4 tuần đủ mẫu sau một vòng sửa, trình đề xuất dừng.</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CPromt Kiếm Tông | V2 hiệu chỉnh | Trang &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;CPromt Kiếm Tông | Dashboard v2 | Trang &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -961,7 +961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -975,14 +975,14 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>ĐỐI CHIẾU V1 → V2 — GIỮ NGUYÊN FILE V1</t>
+          <t>ĐỐI CHIẾU THAY ĐỔI GIỮA DASHBOARD V1 VÀ V2</t>
         </is>
       </c>
     </row>
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Góp ý Nhóm 05 theo bản nhóm ghi, chưa kèm biên bản. Các sửa rà soát bổ sung không được gán thành góp ý Nhóm 05.</t>
+          <t>Nhóm: Promt Kiếm Tông | Các thay đổi về chỉ số, bàn giao, nguồn đo và trách nhiệm sau phản biện chéo</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Theo bản nhóm: prompt cao/Like không chứng minh chất lượng; cần biên bản xác nhận.</t>
+          <t>Số prompt cao và lượt Like không chứng minh chất lượng kết quả.</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Chuyển sang chất lượng và kết quả thực của workflow; không gọi activity là vô dụng trong mọi mục đích.</t>
+          <t>Đo chất lượng và kết quả của workflow để hỗ trợ quyết định triển khai.</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>Theo bản nhóm: cần chốt chặn khi câu hỏi phức tạp hoặc nguồn thiếu; chưa kèm biên bản.</t>
+          <t>Cần điểm bàn giao khi câu hỏi phức tạp hoặc nguồn thiếu.</t>
         </is>
       </c>
       <c r="F6" s="15" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Theo bản nhóm: chỉ số cần nguồn thực tế; cần xác nhận nội dung phản biện nhận về.</t>
+          <t>Chỉ số cần nguồn dữ liệu có thể đối chiếu trong workflow.</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Chưa có baseline thì không báo kết quả. 120 giờ/tháng là mục tiêu đề xuất.</t>
+          <t>Đánh giá mục tiêu 120 giờ tiết kiệm ròng/tháng từ log tác vụ và công sức bổ sung.</t>
         </is>
       </c>
     </row>
@@ -1145,49 +1145,18 @@
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>Theo bản nhóm: hành động cần owner/thời hạn; cần biên bản.</t>
+          <t>Hành động cần owner và thời hạn xử lý cụ thể.</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>Phân biệt vai trò đơn vị vận hành với thành viên điều phối bài nhóm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="170" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Hiệu chỉnh theo yêu cầu 16/10/2026</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Các file v2 cũ lệch target, kỳ đo 18%, mô tả 65%; thiếu nguồn số liệu.</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>Thống nhất 6 chỉ số/5 tầng; ghi chưa xác minh, định nghĩa mẫu/gate; bỏ confidence 85% và accuracy 99% chưa kiểm định.</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Rà soát bổ sung theo Yeucau.md; không gán cho Nhóm 05.</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>V1 không sửa. Cần nhóm bổ sung case thực tế và bằng chứng trước khi xác nhận đạt toàn bộ đề bài.</t>
-        </is>
-      </c>
-    </row>
+          <t>Xác định trách nhiệm dữ liệu, kiểm tra chất lượng và xử lý ngoại lệ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="170" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A4:F9"/>
+  <autoFilter ref="A4:F8"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -1197,7 +1166,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CPromt Kiếm Tông | V2 hiệu chỉnh | Trang &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;CPromt Kiếm Tông | Dashboard v2 | Trang &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1232,7 +1201,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Mục tiêu đề xuất, baseline chờ xác nhận. Ngưỡng gate phải đồng thời đạt; thiếu dữ liệu không coi là đạt.</t>
+          <t>Công thức, mẫu đo và cách xử lý dữ liệu thiếu cho sáu chỉ số trong dashboard</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1257,12 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Mẫu số=0 → N/A. Quy mô 25 theo bài nhóm, phải xác nhận; không suy số người từ 18%.</t>
+          <t>Mẫu số bằng 0: N/A. Ghi số người thực tế và dùng cùng định nghĩa trong mọi kỳ đo.</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Chủ quy trình xác nhận phạm vi và ngày đo tại Gate 30. Đây là usage trong workflow, không phải adoption.</t>
+          <t>Chủ quy trình khóa phạm vi và kỳ đo tại Gate 30; mức dùng được theo dõi theo tuần.</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1412,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CPromt Kiếm Tông | V2 hiệu chỉnh | Trang &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;CPromt Kiếm Tông | Dashboard v2 | Trang &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1478,7 +1447,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Vai trò nghiệp vụ cần được đơn vị xác nhận; sinh viên chỉ điều phối bài nhóm. Mục tiêu phải xác nhận ở Gate 30.</t>
+          <t>Mỗi gate có owner, bằng chứng và điều kiện chuyển; mục tiêu được phê duyệt tại Gate 30.</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1498,12 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>Xác nhận case thật; khóa phạm vi/nguồn, bổ nhiệm owner; duyệt quyền, ngân sách, hỗ trợ và nơi lưu log. Baseline ≥50 lượt thủ công tương đương; bộ thử ≥100 câu gồm ≥20 ca cần chuyển.</t>
+          <t>Khóa phạm vi/nguồn, bổ nhiệm owner; duyệt quyền, ngân sách, hỗ trợ và nơi lưu log. Baseline ≥50 lượt thủ công tương đương; bộ thử ≥100 câu gồm ≥20 ca cần chuyển.</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Trích nguồn ≥95%; bàn giao đúng 100% ca thử; đủ baseline/owner/nguồn lực; không lỗi nghiêm trọng chưa xử lý. Mức dùng, hành vi, thời gian và giờ ròng: khóa baseline/kiểm tính khả thi, chưa đặt kết quả đã đạt.</t>
+          <t>Trích nguồn ≥95%; bàn giao đúng 100% ca thử; đủ baseline/owner/nguồn lực; không lỗi nghiêm trọng chưa xử lý. Mức dùng, hành vi, thời gian và giờ ròng: khóa baseline và kiểm tra tính khả thi.</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -1588,7 +1557,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>Đạt đủ → đề xuất mở rộng từng đợt sau phê duyệt; không tự đặt quy mô 200 người hoặc tuyên bố normalization.</t>
+          <t>Đạt đủ điều kiện: trình phê duyệt mở rộng từng đợt theo ngân sách và năng lực vận hành.</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -1608,7 +1577,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CPromt Kiếm Tông | V2 hiệu chỉnh | Trang &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;CPromt Kiếm Tông | Dashboard v2 | Trang &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1623,7 +1592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1636,14 +1605,14 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>TRẠNG THÁI BẰNG CHỨNG VÀ VIỆC CẦN NHÓM BỔ SUNG</t>
+          <t>KẾ HOẠCH THU THẬP DỮ LIỆU VÀ NGUỒN THAM KHẢO</t>
         </is>
       </c>
     </row>
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Nhóm xác nhận chưa có bằng chứng kèm theo khi rà soát. Không công bố log nhạy cảm; dùng bản tổng hợp đã ẩn danh.</t>
+          <t>Thu thập baseline trong giai đoạn 0–30 ngày; tổng hợp hằng tuần và đánh giá giá trị theo tháng.</t>
         </is>
       </c>
     </row>
@@ -1662,216 +1631,190 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>Hiện có</t>
+          <t>Dữ liệu cần thu thập</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>Trạng thái</t>
+          <t>Thời điểm / cỡ mẫu</t>
         </is>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>Cần bổ sung / giới hạn</t>
+          <t>Cách đối chiếu</t>
         </is>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
-          <t>Người điều phối</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="170" customHeight="1">
+          <t>Người phụ trách</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="150" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>Case thực tế và 25 người</t>
+          <t>Mức dùng</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>Mô tả tình huống trong bài nhóm; chưa có căn cứ đính kèm.</t>
+          <t>Người có tác vụ AI gắn ticket; người được phân công tác vụ đủ điều kiện.</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>Chưa xác minh</t>
+          <t>Gate 30 khóa baseline; tổng hợp hằng tuần.</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Xác nhận tình huống từ lớp/doanh nghiệp; nguồn ghi nhận, thời điểm, phạm vi. Không dùng case tưởng tượng theo §3.1.</t>
+          <t>Đối chiếu log tác vụ với lịch phân công, ghi cả tử số và mẫu số.</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Trần Đình Hinh điều phối; Chủ quy trình xác nhận.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>18% quay lại</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>README: sau 2 tuần; memo cũ: sau 4 tuần; Excel cũ: tuần 1.</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Chưa xác minh; không khớp kỳ đo, thiếu tử/mẫu số</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>Định nghĩa quay lại, ngày đo và số người đủ điều kiện. 18% không tương ứng số nguyên người trên 25; không sửa thành số mới khi thiếu log.</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>Trần Đình Hinh điều phối, đối chiếu log.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="170" customHeight="1">
+          <t>Chủ quy trình Vận hành</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Hành vi và năng suất</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Trạng thái hoàn tất/duyệt; hỏi thêm, làm lại; phút lao động từng đoạn và loại tác vụ.</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Baseline ≥50 lượt thủ công; pilot ≥50 tác vụ đủ theo dõi/tuần, cộng 2 ngày theo dõi sửa.</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>Đối chiếu ticket_id, loại/độ khó và thời gian từng đoạn; cộng công sức chuyển/làm lại.</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Chủ quy trình Vận hành</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8,5 phút; 22%; trích nguồn/handoff 0%</t>
+          <t>Chất lượng trích nguồn</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Có số trong bản nhóm, chưa có tập đo.</t>
+          <t>Câu trả lời, link văn bản, điều khoản, hiệu lực và kết quả chấm QA.</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>Chưa xác minh; baseline hiện tại phải đo lại/xác nhận</t>
+          <t>Gate 30: ≥100 câu thử, gồm ≥20 ca cần chuyển; vận hành QA ngẫu nhiên ≥50 câu/tuần hoặc toàn bộ nếu ít hơn.</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>Log tác vụ đã ẩn danh, phương pháp đo theo Định nghĩa đo; thiếu dữ liệu không suy ra 0%.</t>
+          <t>QA đối chiếu nguồn chuẩn; ca rủi ro kiểm riêng ngoài mẫu ngẫu nhiên.</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Đinh Xuân Quyền tổng hợp; Hoàng Quốc Dũng cùng QA đối chiếu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="170" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>65%; 450 phiên; phỏng vấn 10/10</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>Các bản mô tả khác nhau về kỳ và tiêu chí bỏ dở; chưa có log/ghi nhận.</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Chưa xác minh; không dùng làm kết quả đã chứng minh</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>Đính kèm bản tổng hợp có ngày, mẫu, định nghĩa, câu hỏi phỏng vấn và người tổng hợp; không tự tạo lời trích dẫn.</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>Nhóm trưởng xác nhận với người thu thập.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="170" customHeight="1">
+          <t>QA; AI Tech Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="150" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Bàn giao</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Lý do chuyển, ngữ cảnh, ticket_id, người nhận và thời điểm tạo/nhận.</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Toàn bộ ca cần chuyển và bộ thử Gate 30.</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Rà ca được gắn cờ cùng ca bỏ sót do QA phát hiện; so SLA 4 giờ làm việc.</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Chủ quy trình Vận hành; AI Tech Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="150" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>Phản biện Nhóm 05</t>
+          <t>Giá trị</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Có mô tả góp ý trong bài, chưa kèm biên bản.</t>
+          <t>Lưu lượng theo loại tác vụ, phút baseline/thực tế, công sức QA/bảo trì/hỗ trợ tăng thêm.</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>Theo bài nhóm ghi; chưa xác minh</t>
+          <t>Gate 30 kiểm tính khả thi; Gate 60/90 dùng một tháng đủ dữ liệu.</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>Ghi riêng góp ý đã đưa đi và ≥2 góp ý nhận về, người tham gia và sửa tương ứng. V1 được giữ nguyên để đối chiếu.</t>
+          <t>Tính giờ ròng theo Định nghĩa đo; không cộng trùng công sức đã tính trong tác vụ.</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Nhóm trưởng xác nhận.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="170" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+          <t>Chủ quy trình Vận hành</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Case tham khảo Morgan Stanley</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>https://openai.com/index/morgan-stanley/</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Đã kiểm tra nguồn ngày 16/10/2026</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>Nguồn mô tả eval trước triển khai, chuyên gia chấm, QA hồi quy và người kiểm. Hỗ trợ lựa chọn thiết kế, không xác nhận hiện trạng nội bộ hoặc quan hệ nhân quả riêng của citations.</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>Suy luận áp dụng của nhóm, không phải log doanh nghiệp nhóm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="170" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Mục tiêu ≥120 giờ/tháng</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>Chưa có baseline, lưu lượng và công sức tăng thêm.</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Mục tiêu đề xuất; chưa phải kết quả/ROI</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>Kiểm định lượng tác vụ và phút tiết kiệm ròng; chốt mục tiêu có thể thu thập và nguồn lực tại Gate 30.</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Chủ quy trình Vận hành phê duyệt.</t>
-        </is>
-      </c>
-    </row>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Nguồn tham khảo về đánh giá và kiểm soát chất lượng AI.</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Bài học áp dụng: đánh giá trước triển khai, chuyên gia chấm, QA hồi quy và người kiểm đầu ra.</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Nhóm Promt Kiếm Tông</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="170" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A4:E11"/>
+  <autoFilter ref="A4:E10"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -1884,7 +1827,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CPromt Kiếm Tông | V2 hiệu chỉnh | Trang &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;CPromt Kiếm Tông | Dashboard v2 | Trang &amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
